--- a/BMS_finances.xlsx
+++ b/BMS_finances.xlsx
@@ -35,20 +35,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
+        <fgColor rgb="0098FB98"/>
+        <bgColor rgb="0098FB98"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-        <bgColor rgb="00FF0000"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000FF00"/>
-        <bgColor rgb="0000FF00"/>
+        <fgColor rgb="00ADD8E6"/>
+        <bgColor rgb="00ADD8E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,47 +455,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>500</v>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+7500</t>
+          <t>+0</t>
         </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C3" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2000</v>
       </c>
     </row>
   </sheetData>
